--- a/data/trans_dic/P57_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P57_R2-Estudios-trans_dic.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10)</t>
+          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,5; 26,82</t>
+          <t>20,71; 26,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,43; 37,71</t>
+          <t>29,54; 37,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,41; 20,57</t>
+          <t>15,77; 20,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,23; 29,56</t>
+          <t>24,27; 29,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,64; 22,42</t>
+          <t>18,53; 22,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,18; 31,88</t>
+          <t>27,21; 31,73</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,63; 32,82</t>
+          <t>28,76; 32,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49,24; 71,34</t>
+          <t>49,01; 69,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,32; 30,43</t>
+          <t>26,35; 30,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,67; 44,95</t>
+          <t>28,58; 45,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,17; 31,0</t>
+          <t>28,01; 31,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,56; 55,94</t>
+          <t>41,82; 56,15</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,42; 42,82</t>
+          <t>34,36; 43,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43,88; 52,4</t>
+          <t>43,71; 52,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,82; 38,23</t>
+          <t>30,48; 38,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42,11; 48,88</t>
+          <t>41,94; 48,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,49; 39,5</t>
+          <t>33,35; 39,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,85; 49,38</t>
+          <t>43,67; 49,4</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,99; 32,0</t>
+          <t>28,78; 32,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,31; 62,09</t>
+          <t>46,31; 62,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,01; 28,0</t>
+          <t>24,98; 28,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,91; 41,13</t>
+          <t>31,63; 41,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,22; 29,44</t>
+          <t>27,38; 29,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,67; 49,79</t>
+          <t>40,41; 50,55</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10)</t>
+          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1101,32 +1101,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>154219; 201775</t>
+          <t>155794; 201980</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>149308; 191313</t>
+          <t>149850; 190991</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>152683; 203894</t>
+          <t>156309; 206239</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>180074; 219643</t>
+          <t>180344; 221368</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>324898; 390804</t>
+          <t>322990; 393378</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>339947; 398634</t>
+          <t>340319; 396847</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1219,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>591671; 678246</t>
+          <t>594521; 677323</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1126693; 1632476</t>
+          <t>1121467; 1593610</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>520736; 602110</t>
+          <t>521342; 605980</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>617365; 1002881</t>
+          <t>637725; 1008079</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1139476; 1253962</t>
+          <t>1133049; 1255656</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1878211; 2528382</t>
+          <t>1889966; 2537543</t>
         </is>
       </c>
     </row>
@@ -1337,32 +1337,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>182101; 233327</t>
+          <t>187218; 234505</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>283495; 338535</t>
+          <t>282352; 337939</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>162800; 208717</t>
+          <t>166382; 209261</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>277308; 321836</t>
+          <t>276190; 321336</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>365358; 430897</t>
+          <t>363806; 428381</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>572059; 644163</t>
+          <t>569675; 644395</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1455,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>975293; 1076395</t>
+          <t>968129; 1076662</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1593769; 2136940</t>
+          <t>1593927; 2153807</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>879365; 984428</t>
+          <t>878187; 984628</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1122808; 1494255</t>
+          <t>1149128; 1503499</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1872948; 2025357</t>
+          <t>1883447; 2025882</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2876969; 3522634</t>
+          <t>2858620; 3576247</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P57_R2-Estudios-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,39%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,71; 26,85</t>
+          <t>20,59; 26,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,54; 37,64</t>
+          <t>30,45; 38,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,77; 20,81</t>
+          <t>15,49; 20,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,27; 29,79</t>
+          <t>23,79; 28,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,53; 22,57</t>
+          <t>18,34; 22,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,21; 31,73</t>
+          <t>27,28; 31,69</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,51%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,76; 32,77</t>
+          <t>28,84; 33,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49,01; 69,64</t>
+          <t>46,81; 51,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,35; 30,62</t>
+          <t>26,41; 30,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,58; 45,18</t>
+          <t>43,72; 47,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,01; 31,04</t>
+          <t>28,04; 30,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,82; 56,15</t>
+          <t>45,92; 48,99</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,08%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,36; 43,03</t>
+          <t>34,42; 42,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43,71; 52,31</t>
+          <t>43,08; 51,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,48; 38,33</t>
+          <t>29,97; 38,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41,94; 48,8</t>
+          <t>41,06; 47,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,35; 39,27</t>
+          <t>33,21; 39,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,67; 49,4</t>
+          <t>43,51; 48,94</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>43,76%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,78; 32,01</t>
+          <t>28,96; 32,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,31; 62,58</t>
+          <t>44,46; 48,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,98; 28,01</t>
+          <t>24,91; 28,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,63; 41,39</t>
+          <t>39,88; 42,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,38; 29,45</t>
+          <t>27,2; 29,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,41; 50,55</t>
+          <t>42,58; 44,95</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>169501</t>
+          <t>193206</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>199238</t>
+          <t>212265</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>368740</t>
+          <t>405471</t>
         </is>
       </c>
     </row>
@@ -1101,32 +1101,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>155794; 201980</t>
+          <t>154904; 201440</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>149850; 190991</t>
+          <t>173655; 218672</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>156309; 206239</t>
+          <t>153510; 204738</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>180344; 221368</t>
+          <t>192556; 230209</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>322990; 393378</t>
+          <t>319762; 386685</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>340319; 396847</t>
+          <t>376468; 437212</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1264830</t>
+          <t>1095798</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>882649</t>
+          <t>991082</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2147479</t>
+          <t>2086880</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1219,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>594521; 677323</t>
+          <t>596106; 683037</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1121467; 1593610</t>
+          <t>1043140; 1150417</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>521342; 605980</t>
+          <t>522648; 601460</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>637725; 1008079</t>
+          <t>946308; 1035792</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1133049; 1255656</t>
+          <t>1134446; 1252575</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1889966; 2537543</t>
+          <t>2017116; 2151967</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>308808</t>
+          <t>338246</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>298900</t>
+          <t>327067</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>607709</t>
+          <t>665313</t>
         </is>
       </c>
     </row>
@@ -1337,32 +1337,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>187218; 234505</t>
+          <t>187539; 232788</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>282352; 337939</t>
+          <t>306290; 367454</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>166382; 209261</t>
+          <t>163595; 209833</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>276190; 321336</t>
+          <t>300891; 349758</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>363806; 428381</t>
+          <t>362323; 429507</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>569675; 644395</t>
+          <t>628147; 706542</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1743139</t>
+          <t>1627250</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1380788</t>
+          <t>1530414</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3123927</t>
+          <t>3157664</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1455,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>968129; 1076662</t>
+          <t>974106; 1080666</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1593927; 2153807</t>
+          <t>1560587; 1694637</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>878187; 984628</t>
+          <t>875801; 986897</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1149128; 1503499</t>
+          <t>1478100; 1582434</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1883447; 2025882</t>
+          <t>1871145; 2027365</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2858620; 3576247</t>
+          <t>3072930; 3243434</t>
         </is>
       </c>
     </row>
